--- a/ig/main/CodeSystem-tre-r392-type-act-smsse-regulee.xlsx
+++ b/ig/main/CodeSystem-tre-r392-type-act-smsse-regulee.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14872" uniqueCount="9937">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14893" uniqueCount="9951">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260827120000</t>
+    <t>20260928120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T12:00:00+01:00</t>
+    <t>2026-09-28T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -124,7 +124,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>4914</t>
+    <t>4921</t>
   </si>
   <si>
     <t>Code</t>
@@ -23459,6 +23459,48 @@
   </si>
   <si>
     <t>AMSR/965/43/700</t>
+  </si>
+  <si>
+    <t>72537</t>
+  </si>
+  <si>
+    <t>AMSR/508/11/840</t>
+  </si>
+  <si>
+    <t>72538</t>
+  </si>
+  <si>
+    <t>AMSR/508/11/841</t>
+  </si>
+  <si>
+    <t>72539</t>
+  </si>
+  <si>
+    <t>AMSR/508/16/841</t>
+  </si>
+  <si>
+    <t>72540</t>
+  </si>
+  <si>
+    <t>AMSR/570/11/441</t>
+  </si>
+  <si>
+    <t>72541</t>
+  </si>
+  <si>
+    <t>AMSR/570/40/441</t>
+  </si>
+  <si>
+    <t>72542</t>
+  </si>
+  <si>
+    <t>AMSR/962/11/441</t>
+  </si>
+  <si>
+    <t>72543</t>
+  </si>
+  <si>
+    <t>AMSR/962/40/441</t>
   </si>
   <si>
     <t>80001</t>
@@ -30454,7 +30496,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D4915"/>
+  <dimension ref="A1:D4922"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -89439,6 +89481,90 @@
       </c>
       <c r="D4915" s="2"/>
     </row>
+    <row r="4916">
+      <c r="A4916" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B4916" t="s" s="2">
+        <v>9937</v>
+      </c>
+      <c r="C4916" t="s" s="2">
+        <v>9938</v>
+      </c>
+      <c r="D4916" s="2"/>
+    </row>
+    <row r="4917">
+      <c r="A4917" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B4917" t="s" s="2">
+        <v>9939</v>
+      </c>
+      <c r="C4917" t="s" s="2">
+        <v>9940</v>
+      </c>
+      <c r="D4917" s="2"/>
+    </row>
+    <row r="4918">
+      <c r="A4918" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B4918" t="s" s="2">
+        <v>9941</v>
+      </c>
+      <c r="C4918" t="s" s="2">
+        <v>9942</v>
+      </c>
+      <c r="D4918" s="2"/>
+    </row>
+    <row r="4919">
+      <c r="A4919" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B4919" t="s" s="2">
+        <v>9943</v>
+      </c>
+      <c r="C4919" t="s" s="2">
+        <v>9944</v>
+      </c>
+      <c r="D4919" s="2"/>
+    </row>
+    <row r="4920">
+      <c r="A4920" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B4920" t="s" s="2">
+        <v>9945</v>
+      </c>
+      <c r="C4920" t="s" s="2">
+        <v>9946</v>
+      </c>
+      <c r="D4920" s="2"/>
+    </row>
+    <row r="4921">
+      <c r="A4921" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B4921" t="s" s="2">
+        <v>9947</v>
+      </c>
+      <c r="C4921" t="s" s="2">
+        <v>9948</v>
+      </c>
+      <c r="D4921" s="2"/>
+    </row>
+    <row r="4922">
+      <c r="A4922" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B4922" t="s" s="2">
+        <v>9949</v>
+      </c>
+      <c r="C4922" t="s" s="2">
+        <v>9950</v>
+      </c>
+      <c r="D4922" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
